--- a/registro_rentabilidad.xlsx
+++ b/registro_rentabilidad.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historico" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -563,10 +564,15 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Fecha Reporte</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -575,7 +581,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -606,6 +612,11 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>11,8</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -623,19 +634,24 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Marzo 2026</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>Rentabilidad extraida parcialmente</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>LTV y Leverage estan en grafico de barras (numeros no asociables de forma confiable a la columna vigente); Rentabilidad 12M / Dividend Yield / TIR son sobre valor libro, no bursatil.</t>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Rentabilidad 12M / Dividend Yield / TIR son sobre valor libro, no bursatil. LTV leido de las etiquetas de dato del grafico 'Loan to Value Total (LTV)' (por posicion, no por orden de lectura del texto). Leverage esta en un grafico cuya unica linea es 'Tasa promedio deuda financiera' (no Leverage en si) -&gt; se deja vacio para no cargar el dato equivocado.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -710,10 +726,15 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Serie A (fondo tambien reporta Serie I en el PDF)</t>
         </is>
@@ -722,7 +743,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -740,12 +761,12 @@
           <t>20260508_Rentas Inmobiliarias.pdf</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Sitio bloquea automatizacion (HTTP 403, Cloudflare/anti-bot bancario)</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>El archivo actual es el Reglamento Interno del fondo, no la ficha. Descarga manual requerida desde https://banco.bice.cl/inversiones/fondos-de-inversion/bice-rentas-inmobiliarias-fondo-de-inversion y guardar en 'Fondos Descargados/BICE/Rentas Inmobiliarias/'.</t>
         </is>
@@ -754,7 +775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -772,12 +793,12 @@
           <t>20260508_Rentas Residenciales.pdf</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>PDF sin capa de texto (parece escaneado / imagen)</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>pdfplumber no pudo extraer ningun texto del documento. Para OCR falta instalar: pip install pytesseract pdf2image, + Tesseract-OCR y poppler en el PATH. Alternativa: buscar una version nativa (no escaneada) en santanderassetmanagement.cl.</t>
         </is>
@@ -786,7 +807,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -824,12 +845,12 @@
           <t>29,07</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Serie I (primera serie reportada en la tabla del fondo)</t>
         </is>
@@ -838,7 +859,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -888,10 +909,15 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Septiembre 2025</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Dividend Yield sobre valor bolsa; ver PDF para Dividend Yield sobre NAV</t>
         </is>
@@ -900,7 +926,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -918,12 +944,12 @@
           <t>20260507_Patio Oficinas II.pdf</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Se descargo el documento equivocado (carta a aportantes, no el factsheet)</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Reintentar descarga desde la pagina del fondo en larrainvial.com; este PDF es una carta sobre la auditoria forense de Grupo Patio/Factop.</t>
         </is>
@@ -932,7 +958,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,10 +1003,15 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Septiembre 2025</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Dividend Yield sobre valor bolsa; ver PDF para Dividend Yield sobre NAV</t>
         </is>
@@ -989,7 +1020,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,10 +1055,15 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Diciembre 2025</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Dividend Yield sobre valor bolsa; ver PDF para Dividend Yield sobre NAV</t>
         </is>
@@ -1036,7 +1072,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1067,7 +1103,7 @@
       <c r="U11" t="n">
         <v>36</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>El factsheet no incluye la tabla de indicadores de rentabilidad (fondo joven / informe reducido)</t>
         </is>
@@ -1076,7 +1112,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1136,10 +1172,15 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Octubre 2025</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Serie principal del fondo (puede haber otras series con valores distintos)</t>
         </is>
@@ -1148,7 +1189,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1208,10 +1249,15 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Enero 2026</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Serie principal del fondo (puede haber otras series con valores distintos)</t>
         </is>
@@ -1220,7 +1266,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1280,10 +1326,15 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Enero 2026</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Serie principal del fondo (puede haber otras series con valores distintos)</t>
         </is>
@@ -1292,7 +1343,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1357,10 +1408,15 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Enero 2026</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>OK - rentabilidad extraida</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Serie principal del fondo (puede haber otras series con valores distintos)</t>
         </is>
@@ -1369,7 +1425,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,12 +1448,12 @@
           <t>CLP</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Folleto Informativo tipo KIID: trae 'Mejores y Peores Rentabilidades Ultimos 5 anos' como grafico de barras sin etiquetas de periodo en el texto extraido.</t>
         </is>
@@ -1406,7 +1462,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1424,12 +1480,12 @@
           <t>20260825_FIX_EEFF.pdf</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>La administradora no publica factsheet/ficha para este fondo</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Se descargaron los Estados Financieros como mejor alternativa disponible; no contienen rentabilidad periodica lista para usar.</t>
         </is>
@@ -1438,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1466,12 +1522,12 @@
           <t>12 años</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Informe mensual exportado de Power BI: solo trae graficos (valor cuota, dividendos), sin tabla numerica de rentabilidad.</t>
         </is>
@@ -1480,7 +1536,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1498,12 +1554,12 @@
           <t>20260825_FIX_EEFF.pdf</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>La administradora no publica factsheet/ficha para este fondo</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Se descargaron los Estados Financieros como mejor alternativa disponible; no contienen rentabilidad periodica lista para usar.</t>
         </is>
@@ -1512,7 +1568,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1540,12 +1596,12 @@
           <t>7 años</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Informe mensual exportado de Power BI: solo trae graficos (valor cuota, dividendos), sin tabla numerica de rentabilidad.</t>
         </is>
@@ -1554,7 +1610,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1582,12 +1638,12 @@
           <t>8 años</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Informe mensual exportado de Power BI: solo trae graficos (valor cuota, dividendos), sin tabla numerica de rentabilidad.</t>
         </is>
@@ -1596,7 +1652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1614,12 +1670,12 @@
           <t>20260825_FIX_EEFF.pdf</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>La administradora no publica factsheet/ficha para este fondo</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Se descargaron los Estados Financieros como mejor alternativa disponible; no contienen rentabilidad periodica lista para usar.</t>
         </is>
@@ -1628,7 +1684,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1646,12 +1702,12 @@
           <t>20260825_FIX_EEFF.pdf</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>La administradora no publica factsheet/ficha para este fondo</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Se descargaron los Estados Financieros como mejor alternativa disponible; no contienen rentabilidad periodica lista para usar.</t>
         </is>
@@ -1660,22 +1716,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Frontal Trust</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Renta Residencial</t>
+          <t>Fundamenta Plaza Egaña</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20260825_FIX_FolletoSerieA.pdf</t>
+          <t>20260508_Fundamenta Plaza Egaña.pdf</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -1685,104 +1741,86 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10 años</t>
+          <t>9 años</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Folleto Informativo tipo KIID (LVA Indices): 'Mejores y Peores Rentabilidades Ultimos 5 anos' como grafico de barras sin etiquetas de periodo en el texto extraido.</t>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Banchile</t>
+          <t>Frontal Trust</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Desarrollo y Rentas Residenciales</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20260508_Desarrollo y Rentas Residenciales.pdf</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>-0,04</t>
+          <t>20260508_San Bernardo.pdf</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>UF</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>4</v>
+          <t>CLP</t>
+        </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>OK - rentabilidad extraida</t>
+          <t>2026-Mar</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Banchile</t>
+          <t>Frontal Trust</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inmobiliario X</t>
+          <t>Desarrollos Industriales I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20260508_Inmobiliario X.pdf</t>
+          <t>20260508_Desarrollos Industriales I.pdf</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -1790,410 +1828,493 @@
           <t>CLP</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>5 años</t>
-        </is>
-      </c>
       <c r="V26" t="inlineStr">
         <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Este fondo solo trae el grafico de evolucion de valor cuota, sin la tabla numerica 'Rentabilidad del Fondo'.</t>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Banchile</t>
+          <t>Frontal Trust</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inmobiliario XI</t>
+          <t>Desarrollo Inmobiliario XIII</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20260508_Inmobiliario XI.pdf</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>8,38</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2,96</t>
+          <t>20260508_Desarrollo Inmobiliario XIII.pdf</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>UF</t>
-        </is>
-      </c>
-      <c r="U27" t="n">
-        <v>28</v>
+          <t>CLP</t>
+        </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>OK - rentabilidad extraida</t>
+          <t>2026-Ene</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica. El PDF menciona una formula contractual de rentabilidad objetivo (UF+8,0% anual, Distribucion Extraordinaria), no un resultado medido; no se carga en ninguna columna.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Banchile</t>
+          <t>Frontal Trust</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inmobiliario IX</t>
+          <t>Desarrollo Inmobiliario XV</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20260508_Inmobiliario IX.pdf</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-5,30</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>-4,82</t>
+          <t>20260508_Desarrollo Inmobiliario XV.pdf</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>UF</t>
-        </is>
-      </c>
-      <c r="U28" t="n">
-        <v>4</v>
+          <t>CLP</t>
+        </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>OK - rentabilidad extraida</t>
+          <t>2025-Dic</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Credicorp</t>
+          <t>Frontal Trust</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Renta Residencial I</t>
+          <t>Desarrollo Inmobiliario XVI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20260508_Renta Residencial I.pdf</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>9 años</t>
+          <t>20260508_Desarrollo Inmobiliario XVI.pdf</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>CLP</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Credicorp</t>
+          <t>Frontal Trust</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aconcagua II</t>
+          <t>Desarrollo Inmobiliario XX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20260508_Aconcagua II.pdf</t>
+          <t>20260508_Desarrollo Inmobiliario XX.pdf</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>CLP</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>10 años</t>
+          <t>6 años</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Credicorp</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Capital Raíces</t>
+          <t>Renta Residencial</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20260825_FIX_FactSheet.pdf</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
+          <t>20260825_FIX_FolletoSerieA.pdf</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>10 años</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Folleto Informativo tipo KIID (LVA Indices): 'Mejores y Peores Rentabilidades Ultimos 5 anos' como grafico de barras sin etiquetas de periodo en el texto extraido.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Credicorp</t>
+          <t>Banchile</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Renta Residencial II</t>
+          <t>Desarrollo y Rentas Residenciales</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20260508_Renta Residencial II.pdf</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>10 años</t>
-        </is>
+          <t>20260508_Desarrollo y Rentas Residenciales.pdf</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7,15</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>31 deMarzo de 2026</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Credicorp</t>
+          <t>Banchile</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plaza Egaña</t>
+          <t>Inmobiliario X</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20260508_Plaza Egaña.pdf</t>
+          <t>20260508_Inmobiliario X.pdf</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>CLP</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>5 años (16 de junio de 2023)</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
+          <t>5 años</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Este fondo solo trae el grafico de evolucion de valor cuota, sin la tabla numerica 'Rentabilidad del Fondo'.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Credicorp</t>
+          <t>Banchile</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Aconcagua III</t>
+          <t>Inmobiliario XI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20260508_Aconcagua III.pdf</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>7 años</t>
-        </is>
+          <t>20260508_Inmobiliario XI.pdf</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8,38</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2,96</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>28</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>31 deMarzo de 2026</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Credicorp</t>
+          <t>Banchile</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Renta Inmobiliaria II</t>
+          <t>Inmobiliario IX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20260508_Renta Inmobiliaria II.pdf</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>7 años</t>
-        </is>
+          <t>20260508_Inmobiliario IX.pdf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-5,30</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-4,82</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>31 deMarzo de 2026</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2203,34 +2324,34 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Retorno Preferente Maestra I</t>
+          <t>Renta Residencial I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20260508_Retorno Preferente Maestra I.pdf</t>
+          <t>20260508_Renta Residencial I.pdf</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>5 años</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
+          <t>9 años</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2240,34 +2361,39 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Renta Industrial I</t>
+          <t>Aconcagua II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20260508_Renta Industrial I.pdf</t>
+          <t>20260508_Aconcagua II.pdf</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>15,88</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5 años</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>10 años</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+          <t>Rentabilidad extraida parcialmente (mencion suelta en texto libre)</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Rentabilidad 'Desde Inicio' leida del texto libre del comentario (UF), no de una tabla.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2277,34 +2403,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Renta Residencial III</t>
+          <t>Capital Raíces</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20260508_Renta Residencial III.pdf</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>7 años</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
+          <t>20260825_FIX_FactSheet.pdf</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2314,392 +2435,2749 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Preferente Maestra II</t>
+          <t>Renta Residencial II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20260825_FIX_FactSheet.pdf</t>
+          <t>20260508_Renta Residencial II.pdf</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>5 años</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
+          <t>10 años</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica, solo menciones sueltas en el comentario del administrador (rentabilidad esperada o acumulada desde el inicio, no comparable entre fondos).</t>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Credicorp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Asset  Rentas Residenciales</t>
+          <t>Plaza Egaña</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20260508_Asset  Rentas Residenciales.pdf</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Sitio caido durante el re-scrapeo (assetagf.com no respondio)</t>
+          <t>20260508_Plaza Egaña.pdf</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5 años (16 de junio de 2023)</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos (documento incorrecto, sin datos de rentabilidad). Reintentar navegando a la pestaña especifica de cada fondo en https://assetagf.com/fondos-de-inversion/</t>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Credicorp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Asset Outlets Vivo</t>
+          <t>Aconcagua III</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20260508_Asset Outlets Vivo.pdf</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Sitio caido durante el re-scrapeo (assetagf.com no respondio)</t>
+          <t>20260508_Aconcagua III.pdf</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>7 años</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos (documento incorrecto, sin datos de rentabilidad). Reintentar navegando a la pestaña especifica de cada fondo en https://assetagf.com/fondos-de-inversion/</t>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-25 12:54</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Credicorp</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Asset Desarrollo Chamisero</t>
+          <t>Renta Inmobiliaria II</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20260508_Asset Desarrollo Chamisero.pdf</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Sitio caido durante el re-scrapeo (assetagf.com no respondio)</t>
+          <t>20260508_Renta Inmobiliaria II.pdf</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>7 años</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>El archivo actual es un Informe de Auditor de 'Asset Rentas Residenciales' reciclado para los 3 fondos (documento incorrecto, sin datos de rentabilidad). Reintentar navegando a la pestaña especifica de cada fondo en https://assetagf.com/fondos-de-inversion/</t>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-25 12:56</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Frontal Trust</t>
+          <t>Credicorp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fundamenta Plaza Egaña</t>
+          <t>Retorno Preferente Maestra I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20260508_Fundamenta Plaza Egaña.pdf</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>CLP</t>
+          <t>20260508_Retorno Preferente Maestra I.pdf</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>9 años</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
+          <t>5 años</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. El PDF menciona una rentabilidad OBJETIVO (no realizada) de UF+6,4% para el aportante; no se carga en ninguna columna para no confundirla con un resultado medido.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-25 12:56</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Frontal Trust</t>
+          <t>Credicorp</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Renta Industrial I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20260508_San Bernardo.pdf</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
+          <t>20260508_Renta Industrial I.pdf</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-25 12:56</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Frontal Trust</t>
+          <t>Credicorp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Desarrollos Industriales I</t>
+          <t>Renta Residencial III</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20260508_Desarrollos Industriales I.pdf</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
+          <t>20260508_Renta Residencial III.pdf</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7 años</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-25 12:56</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frontal Trust</t>
+          <t>Credicorp</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Desarrollo Inmobiliario XIII</t>
+          <t>Preferente Maestra II</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20260508_Desarrollo Inmobiliario XIII.pdf</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
+          <t>20260825_FIX_FactSheet.pdf</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
         <is>
           <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25 12:56</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Frontal Trust</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Desarrollo Inmobiliario XV</t>
+          <t>Asset  Rentas Residenciales</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20260508_Desarrollo Inmobiliario XV.pdf</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>20260508_Asset  Rentas Residenciales.pdf</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-25 12:56</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Frontal Trust</t>
+          <t>Asset</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Desarrollo Inmobiliario XVI</t>
+          <t>Asset Outlets Vivo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260508_Desarrollo Inmobiliario XVI.pdf</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>20260508_Asset Outlets Vivo.pdf</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-25 12:56</t>
+          <t>2026-09-25 14:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Asset Desarrollo Chamisero</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20260508_Asset Desarrollo Chamisero.pdf</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Fecha actualizacion</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Administradora</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Rent. 1M</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Rent. 3M</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Rent. 6M</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Rent. YTD</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Rent. 12M (1A)</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Rent. 24M (2A)</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Rent. 36M (3A)</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Rent. Desde Inicio</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Yield</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>TIR</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Cap Rate</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>LTV</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Rentabilidad Directa</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Plazo/Duracion</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>N Activos</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Fecha Reporte</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CEFIN Rentas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>20260825_FIX_FichaFECU.pdf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15,0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>8,3</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>11,8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Abril 1995 – vencimiento Abril 2030</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>81</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Marzo 2026</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Rentabilidad extraida parcialmente</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>LTV y Leverage estan en grafico de barras (numeros no asociables de forma confiable a la columna vigente); Rentabilidad 12M / Dividend Yield / TIR son sobre valor libro, no bursatil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BTG Pactual</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Renta Comercial</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20260508_Renta Comercial.pdf</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-12,4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>58,7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-0,7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-0,6</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6,4</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,9</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>hasta 25-07-2030</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Serie A (fondo tambien reporta Serie I en el PDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BICE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Rentas Inmobiliarias</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>20260508_Rentas Inmobiliarias.pdf</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sitio bloquea automatizacion (HTTP 403, Cloudflare/anti-bot bancario)</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>El archivo actual es el Reglamento Interno del fondo, no la ficha. Descarga manual requerida desde https://banco.bice.cl/inversiones/fondos-de-inversion/bice-rentas-inmobiliarias-fondo-de-inversion y guardar en 'Fondos Descargados/BICE/Rentas Inmobiliarias/'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rentas Residenciales</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20260508_Rentas Residenciales.pdf</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>PDF sin capa de texto (parece escaneado / imagen)</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>pdfplumber no pudo extraer ningun texto del documento. Para OCR falta instalar: pip install pytesseract pdf2image, + Tesseract-OCR y poppler en el PATH. Alternativa: buscar una version nativa (no escaneada) en santanderassetmanagement.cl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Princiapl</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Renta Residencial</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20260508_Renta Residencial.pdf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0,14</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>29,07</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Serie I (primera serie reportada en la tabla del fondo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Larrain Vial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Patio Oficinas I</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20260507_Patio Oficinas I.pdf</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>35,88</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>68,24</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,97</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4 años</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Septiembre 2025</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Dividend Yield sobre valor bolsa; ver PDF para Dividend Yield sobre NAV</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Larrain Vial</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Patio Oficinas II</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20260507_Patio Oficinas II.pdf</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Se descargo el documento equivocado (carta a aportantes, no el factsheet)</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Reintentar descarga desde la pagina del fondo en larrainvial.com; este PDF es una carta sobre la auditoria forense de Grupo Patio/Factop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Larrain Vial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Renta Inmobiliaria I</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20260507_Renta Inmobiliaria I.pdf</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>64,09</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Septiembre 2025</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Dividend Yield sobre valor bolsa; ver PDF para Dividend Yield sobre NAV</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Larrain Vial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Patio Stripcenters II</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20260507_Patio Stripcenters II.pdf</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>63,89</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Diciembre 2025</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Dividend Yield sobre valor bolsa; ver PDF para Dividend Yield sobre NAV</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Toesca</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Net Lease Chile II</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20260508_Net Lease Chile II.pdf</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>7 años (17/08/2030)</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>36</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>El factsheet no incluye la tabla de indicadores de rentabilidad (fondo joven / informe reducido)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Toesca</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Renta Residencial</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20260508_Renta Residencial.pdf</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-3,0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-4,1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>66,9</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Octubre 2025</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Serie principal del fondo (puede haber otras series con valores distintos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Toesca</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rentas Inmobiliarias Apoquindo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20260508_Rentas Inmobiliarias Apoquindo.pdf</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>13,2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>13,2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-2,3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>74,1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Enero 2026</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Serie principal del fondo (puede haber otras series con valores distintos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Toesca</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rentas Inmobiliarias</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260508_Rentas Inmobiliarias.pdf</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-8,4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>7,0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>61,9</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1,56</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Enero 2026</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Serie principal del fondo (puede haber otras series con valores distintos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Toesca</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rentas Inmobiliarias Pt Fondo de Inversión</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20260508_Rentas Inmobiliarias Pt Fondo de Inversión.pdf</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8,6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8,6</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-6,4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>11,9</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6,0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>81,2</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,35</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>15 años (30 julio 2032)</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Enero 2026</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Serie principal del fondo (puede haber otras series con valores distintos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Inversiones Security</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rentas Inmobiliarias II</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20260825_FIX_FolletoInformativo.pdf</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Folleto Informativo tipo KIID: trae 'Mejores y Peores Rentabilidades Ultimos 5 anos' como grafico de barras sin etiquetas de periodo en el texto extraido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ameris</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Renta Industrial II</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20260825_FIX_EEFF.pdf</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>La administradora no publica factsheet/ficha para este fondo</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Se descargaron los Estados Financieros como mejor alternativa disponible; no contienen rentabilidad periodica lista para usar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ameris</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Renta Reisdencial</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20260825_FIX_factsheet.pdf</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>12 años</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Informe mensual exportado de Power BI: solo trae graficos (valor cuota, dividendos), sin tabla numerica de rentabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ameris</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rentas y Desarrollos Aconcagua</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20260825_FIX_EEFF.pdf</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>La administradora no publica factsheet/ficha para este fondo</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Se descargaron los Estados Financieros como mejor alternativa disponible; no contienen rentabilidad periodica lista para usar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ameris</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Desarrollo Inmobiliario IX</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20260825_FIX_factsheet.pdf</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>7 años</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Informe mensual exportado de Power BI: solo trae graficos (valor cuota, dividendos), sin tabla numerica de rentabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ameris</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UPC Desarrollo Inmobiliario</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20260825_FIX_factsheet.pdf</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>8 años</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Informe mensual exportado de Power BI: solo trae graficos (valor cuota, dividendos), sin tabla numerica de rentabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ameris</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Desarrollo Inmobiliario Uno</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20260825_FIX_EEFF.pdf</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>La administradora no publica factsheet/ficha para este fondo</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Se descargaron los Estados Financieros como mejor alternativa disponible; no contienen rentabilidad periodica lista para usar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ameris</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Megacentro Buenaventura</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20260825_FIX_EEFF.pdf</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>La administradora no publica factsheet/ficha para este fondo</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Se descargaron los Estados Financieros como mejor alternativa disponible; no contienen rentabilidad periodica lista para usar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Frontal Trust</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fundamenta Plaza Egaña</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20260508_Fundamenta Plaza Egaña.pdf</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>9 años</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Frontal Trust</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20260508_San Bernardo.pdf</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-Mar</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Frontal Trust</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Desarrollos Industriales I</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20260508_Desarrollos Industriales I.pdf</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Frontal Trust</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Desarrollo Inmobiliario XIII</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20260508_Desarrollo Inmobiliario XIII.pdf</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-Ene</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica. El PDF menciona una formula contractual de rentabilidad objetivo (UF+8,0% anual, Distribucion Extraordinaria), no un resultado medido; no se carga en ninguna columna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Frontal Trust</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Desarrollo Inmobiliario XV</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20260508_Desarrollo Inmobiliario XV.pdf</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Frontal Trust</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Desarrollo Inmobiliario XVI</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20260508_Desarrollo Inmobiliario XVI.pdf</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Frontal Trust</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Desarrollo Inmobiliario XX</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20260508_Desarrollo Inmobiliario XX.pdf</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>6 años</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2025-Dic</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Renta Residencial</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20260825_FIX_FolletoSerieA.pdf</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>10 años</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Folleto Informativo tipo KIID (LVA Indices): 'Mejores y Peores Rentabilidades Ultimos 5 anos' como grafico de barras sin etiquetas de periodo en el texto extraido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Banchile</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Desarrollo y Rentas Residenciales</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20260508_Desarrollo y Rentas Residenciales.pdf</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7,15</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>31 deMarzo de 2026</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Banchile</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Inmobiliario X</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20260508_Inmobiliario X.pdf</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Este fondo solo trae el grafico de evolucion de valor cuota, sin la tabla numerica 'Rentabilidad del Fondo'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Banchile</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Inmobiliario XI</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20260508_Inmobiliario XI.pdf</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8,38</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2,96</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>28</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>31 deMarzo de 2026</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Banchile</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Inmobiliario IX</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20260508_Inmobiliario IX.pdf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-5,30</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-4,82</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>31 deMarzo de 2026</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>OK - rentabilidad extraida</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Rentabilidad en UF (el PDF tambien reporta la misma tabla en CLP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Renta Residencial I</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20260508_Renta Residencial I.pdf</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>9 años</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Aconcagua II</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20260508_Aconcagua II.pdf</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>15,88</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>10 años</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rentabilidad extraida parcialmente (mencion suelta en texto libre)</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Rentabilidad 'Desde Inicio' leida del texto libre del comentario (UF), no de una tabla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Capital Raíces</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20260825_FIX_FactSheet.pdf</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Renta Residencial II</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20260508_Renta Residencial II.pdf</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>10 años</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Plaza Egaña</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20260508_Plaza Egaña.pdf</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5 años (16 de junio de 2023)</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Aconcagua III</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20260508_Aconcagua III.pdf</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>7 años</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Renta Inmobiliaria II</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20260508_Renta Inmobiliaria II.pdf</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>7 años</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Retorno Preferente Maestra I</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20260508_Retorno Preferente Maestra I.pdf</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. El PDF menciona una rentabilidad OBJETIVO (no realizada) de UF+6,4% para el aportante; no se carga en ninguna columna para no confundirla con un resultado medido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Renta Industrial I</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20260508_Renta Industrial I.pdf</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Renta Residencial III</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20260508_Renta Residencial III.pdf</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7 años</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Credicorp</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Preferente Maestra II</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>20260825_FIX_FactSheet.pdf</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Asset  Rentas Residenciales</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20260508_Asset  Rentas Residenciales.pdf</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Asset Outlets Vivo</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20260508_Asset Outlets Vivo.pdf</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:36</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Desarrollo Inmobiliario XX</t>
+          <t>Asset Desarrollo Chamisero</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260508_Desarrollo Inmobiliario XX.pdf</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>6 años</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>20260508_Asset Desarrollo Chamisero.pdf</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Informe General de fondo de desarrollo: reporta avance de proyectos por unidad (ventas/escrituras/%construccion), no una tabla de rentabilidad periodica.</t>
+          <t>Se descargo el documento equivocado (Informe de Auditor, no el Folleto Informativo)</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>descargar() no encontro el link correcto dentro de la seccion del fondo; revisar selectores en agentes/asset.py.</t>
         </is>
       </c>
     </row>

--- a/registro_rentabilidad.xlsx
+++ b/registro_rentabilidad.xlsx
@@ -581,7 +581,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -926,7 +926,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1462,7 +1462,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1536,7 +1536,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1610,7 +1610,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1684,7 +1684,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1716,7 +1716,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1763,7 +1763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2020,7 +2020,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2132,7 +2132,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2174,7 +2174,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2244,7 +2244,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2314,7 +2314,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2351,7 +2351,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2393,7 +2393,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2443,6 +2443,11 @@
           <t>20260508_Renta Residencial II.pdf</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>24,21</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
           <t>10 años</t>
@@ -2450,19 +2455,19 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>Rentabilidad calculada desde Valor Cuota (Inicio vs Actual)</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Calculado desde Valor Cuota: 27.280,54 el 29-08-2018 -&gt; 33.885,00 el 30-09-2025. Es variacion de PRECIO de la cuota solamente (no incluye dividendos repartidos en el camino) y no esta anualizada -- no es directamente comparable con 'Desde Inicio' de otras administradoras, que si suele incluir dividendos.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2499,7 +2504,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2536,7 +2541,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2573,7 +2578,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2610,7 +2615,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2647,7 +2652,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2665,6 +2670,11 @@
           <t>20260508_Renta Residencial III.pdf</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17,20</t>
+        </is>
+      </c>
       <c r="T45" t="inlineStr">
         <is>
           <t>7 años</t>
@@ -2672,19 +2682,19 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>Rentabilidad calculada desde Valor Cuota (Inicio vs Actual)</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Calculado desde Valor Cuota: 33.401,71 el 10-08-2022 -&gt; 39.147,70 el 30-09-2025. Es variacion de PRECIO de la cuota solamente (no incluye dividendos repartidos en el camino) y no esta anualizada -- no es directamente comparable con 'Desde Inicio' de otras administradoras, que si suele incluir dividendos.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2721,7 +2731,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2753,7 +2763,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2785,7 +2795,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3110,7 +3120,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3142,7 +3152,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3174,7 +3184,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3293,7 +3303,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3439,7 +3449,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3792,7 +3802,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3829,7 +3839,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3861,7 +3871,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3903,7 +3913,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3935,7 +3945,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3977,7 +3987,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4019,7 +4029,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4051,7 +4061,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4387,7 +4397,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4499,7 +4509,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4681,7 +4691,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4718,7 +4728,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4760,7 +4770,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4792,7 +4802,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4810,6 +4820,11 @@
           <t>20260508_Renta Residencial II.pdf</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>24,21</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
           <t>10 años</t>
@@ -4817,19 +4832,19 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>Rentabilidad calculada desde Valor Cuota (Inicio vs Actual)</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Calculado desde Valor Cuota: 27.280,54 el 29-08-2018 -&gt; 33.885,00 el 30-09-2025. Es variacion de PRECIO de la cuota solamente (no incluye dividendos repartidos en el camino) y no esta anualizada -- no es directamente comparable con 'Desde Inicio' de otras administradoras, que si suele incluir dividendos.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4866,7 +4881,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4903,7 +4918,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4940,7 +4955,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4977,7 +4992,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5014,7 +5029,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5032,6 +5047,11 @@
           <t>20260508_Renta Residencial III.pdf</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17,20</t>
+        </is>
+      </c>
       <c r="T45" t="inlineStr">
         <is>
           <t>7 años</t>
@@ -5039,19 +5059,19 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>OK - documento correcto, pero rentabilidad en formato grafico (no extraible por texto)</t>
+          <t>Rentabilidad calculada desde Valor Cuota (Inicio vs Actual)</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica.</t>
+          <t>Reporte de fondo de desarrollo/en liquidacion: no trae tabla estandar de rentabilidad periodica. Calculado desde Valor Cuota: 33.401,71 el 10-08-2022 -&gt; 39.147,70 el 30-09-2025. Es variacion de PRECIO de la cuota solamente (no incluye dividendos repartidos en el camino) y no esta anualizada -- no es directamente comparable con 'Desde Inicio' de otras administradoras, que si suele incluir dividendos.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5088,7 +5108,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5120,7 +5140,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5152,7 +5172,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-25 14:36</t>
+          <t>2026-09-25 15:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
